--- a/request_forms/029_feral_cat_tnr_request_form--request_forms.xlsx
+++ b/request_forms/029_feral_cat_tnr_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,12 +1102,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'alabama'}</t>
+          <t>alabama</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Alabama'}</t>
+          <t>Alabama</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'alaska'}</t>
+          <t>alaska</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Alaska'}</t>
+          <t>Alaska</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'american_samoa'}</t>
+          <t>american_samoa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'American Samoa'}</t>
+          <t>American Samoa</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'arizona'}</t>
+          <t>arizona</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Arizona'}</t>
+          <t>Arizona</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'arkansas'}</t>
+          <t>arkansas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Arkansas'}</t>
+          <t>Arkansas</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'california'}</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'California'}</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'colorado'}</t>
+          <t>colorado</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Colorado'}</t>
+          <t>Colorado</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'connecticut'}</t>
+          <t>connecticut</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Connecticut'}</t>
+          <t>Connecticut</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'delaware'}</t>
+          <t>delaware</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Delaware'}</t>
+          <t>Delaware</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'district_of_columbia'}</t>
+          <t>district_of_columbia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'District of Columbia'}</t>
+          <t>District of Columbia</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'florida'}</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Florida'}</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'georgia'}</t>
+          <t>georgia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Georgia'}</t>
+          <t>Georgia</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'guam'}</t>
+          <t>guam</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Guam'}</t>
+          <t>Guam</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'hawaii'}</t>
+          <t>hawaii</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Hawaii'}</t>
+          <t>Hawaii</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'idaho'}</t>
+          <t>idaho</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Idaho'}</t>
+          <t>Idaho</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'illinois'}</t>
+          <t>illinois</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Illinois'}</t>
+          <t>Illinois</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'indiana'}</t>
+          <t>indiana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Indiana'}</t>
+          <t>Indiana</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'iowa'}</t>
+          <t>iowa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Iowa'}</t>
+          <t>Iowa</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'kansas'}</t>
+          <t>kansas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Kansas'}</t>
+          <t>Kansas</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'kentucky'}</t>
+          <t>kentucky</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Kentucky'}</t>
+          <t>Kentucky</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'louisiana'}</t>
+          <t>louisiana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Louisiana'}</t>
+          <t>Louisiana</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'maine'}</t>
+          <t>maine</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Maine'}</t>
+          <t>Maine</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'maryland'}</t>
+          <t>maryland</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Maryland'}</t>
+          <t>Maryland</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'massachusetts'}</t>
+          <t>massachusetts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Massachusetts'}</t>
+          <t>Massachusetts</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'michigan'}</t>
+          <t>michigan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Michigan'}</t>
+          <t>Michigan</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'minnesota'}</t>
+          <t>minnesota</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Minnesota'}</t>
+          <t>Minnesota</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'mississippi'}</t>
+          <t>mississippi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Mississippi'}</t>
+          <t>Mississippi</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'missouri'}</t>
+          <t>missouri</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Missouri'}</t>
+          <t>Missouri</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'montana'}</t>
+          <t>montana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Montana'}</t>
+          <t>Montana</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'nebraska'}</t>
+          <t>nebraska</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Nebraska'}</t>
+          <t>Nebraska</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'nevada'}</t>
+          <t>nevada</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Nevada'}</t>
+          <t>Nevada</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'new_hampshire'}</t>
+          <t>new_hampshire</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'New Hampshire'}</t>
+          <t>New Hampshire</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'new_jersey'}</t>
+          <t>new_jersey</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'New Jersey'}</t>
+          <t>New Jersey</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'new_mexico'}</t>
+          <t>new_mexico</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'New Mexico'}</t>
+          <t>New Mexico</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'north_carolina'}</t>
+          <t>north_carolina</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'North Carolina'}</t>
+          <t>North Carolina</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'north_dakota'}</t>
+          <t>north_dakota</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'North Dakota'}</t>
+          <t>North Dakota</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'northern_mariana_islands'}</t>
+          <t>northern_mariana_islands</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Northern Mariana Islands'}</t>
+          <t>Northern Mariana Islands</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'ohio'}</t>
+          <t>ohio</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Ohio'}</t>
+          <t>Ohio</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'oklahoma'}</t>
+          <t>oklahoma</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Oklahoma'}</t>
+          <t>Oklahoma</t>
         </is>
       </c>
     </row>
@@ -1815,12 +1815,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'oregon'}</t>
+          <t>oregon</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Oregon'}</t>
+          <t>Oregon</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'pennsylvania'}</t>
+          <t>pennsylvania</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Pennsylvania'}</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'puerto_rico'}</t>
+          <t>puerto_rico</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Puerto Rico'}</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'rhode_island'}</t>
+          <t>rhode_island</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Rhode Island'}</t>
+          <t>Rhode Island</t>
         </is>
       </c>
     </row>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'south_carolina'}</t>
+          <t>south_carolina</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'South Carolina'}</t>
+          <t>South Carolina</t>
         </is>
       </c>
     </row>
@@ -1900,12 +1900,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'south_dakota'}</t>
+          <t>south_dakota</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'South Dakota'}</t>
+          <t>South Dakota</t>
         </is>
       </c>
     </row>
@@ -1917,12 +1917,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'tennessee'}</t>
+          <t>tennessee</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Tennessee'}</t>
+          <t>Tennessee</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'texas'}</t>
+          <t>texas</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Texas'}</t>
+          <t>Texas</t>
         </is>
       </c>
     </row>
@@ -1951,12 +1951,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'utah'}</t>
+          <t>utah</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Utah'}</t>
+          <t>Utah</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'vermont'}</t>
+          <t>vermont</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Vermont'}</t>
+          <t>Vermont</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'virgin_islands'}</t>
+          <t>virgin_islands</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Virgin Islands'}</t>
+          <t>Virgin Islands</t>
         </is>
       </c>
     </row>
@@ -2002,12 +2002,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'virginia'}</t>
+          <t>virginia</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Virginia'}</t>
+          <t>Virginia</t>
         </is>
       </c>
     </row>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'washington'}</t>
+          <t>washington</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'Washington'}</t>
+          <t>Washington</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2036,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'washington'}</t>
+          <t>west_virginia</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Washington'}</t>
+          <t>West Virginia</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'west_virginia'}</t>
+          <t>wisconsin</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'West Virginia'}</t>
+          <t>Wisconsin</t>
         </is>
       </c>
     </row>
@@ -2070,29 +2070,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'wisconsin'}</t>
+          <t>wyoming</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'Wisconsin'}</t>
+          <t>Wyoming</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>location_state_choices</t>
+          <t>request_status_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'wyoming'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'Wyoming'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'open'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Open'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -2121,12 +2121,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'closed'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'Closed'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -2155,12 +2155,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'scheduled'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'Scheduled'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -2172,29 +2172,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'completed'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'Completed'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>request_status_choices</t>
+          <t>request_category_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_'pending'}</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': 'Pending'}</t>
+          <t>General</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'label':_'general'}</t>
+          <t>feral_cat_spay/neuter</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'label': 'General'}</t>
+          <t>Feral Cat Spay/Neuter</t>
         </is>
       </c>
     </row>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'label':_'feral_cat_spay/neuter'}</t>
+          <t>feral_cat_trap-neuter-release_(tnr)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'label': 'Feral Cat Spay/Neuter'}</t>
+          <t>Feral Cat Trap-Neuter-Release (TNR)</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2240,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'label':_'feral_cat_trap-neuter-release_(tnr)'}</t>
+          <t>feral_cat_adoption</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'label': 'Feral Cat Trap-Neuter-Release (TNR)'}</t>
+          <t>Feral Cat Adoption</t>
         </is>
       </c>
     </row>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'label':_'feral_cat_adoption'}</t>
+          <t>feral_cat_rescue</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'label': 'Feral Cat Adoption'}</t>
+          <t>Feral Cat Rescue</t>
         </is>
       </c>
     </row>
@@ -2274,29 +2274,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'label':_'feral_cat_rescue'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'label': 'Feral Cat Rescue'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>request_category_choices</t>
+          <t>volunteer_license_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>license_1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>License 1</t>
         </is>
       </c>
     </row>
@@ -2308,29 +2308,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'label':_'license_1'}</t>
+          <t>license_2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'label': 'License 1'}</t>
+          <t>License 2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>volunteer_license_choices</t>
+          <t>volunteer_vehicle_license_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'label':_'license_2'}</t>
+          <t>license_1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'label': 'License 2'}</t>
+          <t>License 1</t>
         </is>
       </c>
     </row>
@@ -2342,29 +2342,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'label':_'license_1'}</t>
+          <t>license_2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'label': 'License 1'}</t>
+          <t>License 2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>volunteer_vehicle_license_choices</t>
+          <t>volunteer_vehicle_insurance_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'label':_'license_2'}</t>
+          <t>insured</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'label': 'License 2'}</t>
+          <t>Insured</t>
         </is>
       </c>
     </row>
@@ -2376,29 +2376,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'label':_'insured'}</t>
+          <t>uninsured</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'label': 'Insured'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>volunteer_vehicle_insurance_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>{'label':_'uninsured'}</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>{'label': 'Uninsured'}</t>
+          <t>Uninsured</t>
         </is>
       </c>
     </row>
